--- a/Planned/LGY Dex.xlsx
+++ b/Planned/LGY Dex.xlsx
@@ -1,24 +1,1189 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="22943" windowHeight="9875"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Moves" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="144525"/>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Move</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Pound</t>
+  </si>
+  <si>
+    <t>Mega Punch</t>
+  </si>
+  <si>
+    <t>Pay Day</t>
+  </si>
+  <si>
+    <t>Fire Punch</t>
+  </si>
+  <si>
+    <t>Ice Punch</t>
+  </si>
+  <si>
+    <t>Thunder Punch</t>
+  </si>
+  <si>
+    <t>Scratch</t>
+  </si>
+  <si>
+    <t>Guillotine</t>
+  </si>
+  <si>
+    <t>Razor Wind</t>
+  </si>
+  <si>
+    <t>Swords Dance</t>
+  </si>
+  <si>
+    <t>Gust</t>
+  </si>
+  <si>
+    <t>Wing Attack</t>
+  </si>
+  <si>
+    <t>Whirlwind</t>
+  </si>
+  <si>
+    <t>Fly</t>
+  </si>
+  <si>
+    <t>Vine Whip</t>
+  </si>
+  <si>
+    <t>Stomp</t>
+  </si>
+  <si>
+    <t>Double Kick</t>
+  </si>
+  <si>
+    <t>Mega Kick</t>
+  </si>
+  <si>
+    <t>Sand Attack</t>
+  </si>
+  <si>
+    <t>Headbutt</t>
+  </si>
+  <si>
+    <t>Horn Attack</t>
+  </si>
+  <si>
+    <t>Fury Attack</t>
+  </si>
+  <si>
+    <t>Horn Drill</t>
+  </si>
+  <si>
+    <t>Tackle</t>
+  </si>
+  <si>
+    <t>Body Slam</t>
+  </si>
+  <si>
+    <t>Wrap</t>
+  </si>
+  <si>
+    <t>Take Down</t>
+  </si>
+  <si>
+    <t>Thrash</t>
+  </si>
+  <si>
+    <t>Double-Edge</t>
+  </si>
+  <si>
+    <t>Tail Whip</t>
+  </si>
+  <si>
+    <t>Poison Sting</t>
+  </si>
+  <si>
+    <t>Pin Missile</t>
+  </si>
+  <si>
+    <t>Leer</t>
+  </si>
+  <si>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>Growl</t>
+  </si>
+  <si>
+    <t>Roar</t>
+  </si>
+  <si>
+    <t>Sing</t>
+  </si>
+  <si>
+    <t>Supersonic</t>
+  </si>
+  <si>
+    <t>Disable</t>
+  </si>
+  <si>
+    <t>Acid</t>
+  </si>
+  <si>
+    <t>Ember</t>
+  </si>
+  <si>
+    <t>Flamethrower</t>
+  </si>
+  <si>
+    <t>Water Gun</t>
+  </si>
+  <si>
+    <t>Hydro Pump</t>
+  </si>
+  <si>
+    <t>Surf</t>
+  </si>
+  <si>
+    <t>Ice Beam</t>
+  </si>
+  <si>
+    <t>Blizzard</t>
+  </si>
+  <si>
+    <t>Psybeam</t>
+  </si>
+  <si>
+    <t>Bubble Beam</t>
+  </si>
+  <si>
+    <t>Aurora Beam</t>
+  </si>
+  <si>
+    <t>Hyper Beam</t>
+  </si>
+  <si>
+    <t>Peck</t>
+  </si>
+  <si>
+    <t>Drill Peck</t>
+  </si>
+  <si>
+    <t>Low Kick</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>Seismic Toss</t>
+  </si>
+  <si>
+    <t>Absorb</t>
+  </si>
+  <si>
+    <t>Mega Drain</t>
+  </si>
+  <si>
+    <t>Leech Seed</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>Razor Leaf</t>
+  </si>
+  <si>
+    <t>Solar Beam</t>
+  </si>
+  <si>
+    <t>Poison Powder</t>
+  </si>
+  <si>
+    <t>Stun Spore</t>
+  </si>
+  <si>
+    <t>Sleep Powder</t>
+  </si>
+  <si>
+    <t>Petal Dance</t>
+  </si>
+  <si>
+    <t>String Shot</t>
+  </si>
+  <si>
+    <t>Fire Spin</t>
+  </si>
+  <si>
+    <t>Thunder Shock</t>
+  </si>
+  <si>
+    <t>Thunderbolt</t>
+  </si>
+  <si>
+    <t>Thunder Wave</t>
+  </si>
+  <si>
+    <t>Thunder</t>
+  </si>
+  <si>
+    <t>Rock Throw</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>Fissure</t>
+  </si>
+  <si>
+    <t>Dig</t>
+  </si>
+  <si>
+    <t>Toxic</t>
+  </si>
+  <si>
+    <t>Confusion</t>
+  </si>
+  <si>
+    <t>Psychic</t>
+  </si>
+  <si>
+    <t>Hypnosis</t>
+  </si>
+  <si>
+    <t>Agility</t>
+  </si>
+  <si>
+    <t>Quick Attack</t>
+  </si>
+  <si>
+    <t>Teleport</t>
+  </si>
+  <si>
+    <t>Night Shade</t>
+  </si>
+  <si>
+    <t>Mimic</t>
+  </si>
+  <si>
+    <t>Screech</t>
+  </si>
+  <si>
+    <t>Double Team</t>
+  </si>
+  <si>
+    <t>Recover</t>
+  </si>
+  <si>
+    <t>Harden</t>
+  </si>
+  <si>
+    <t>Minimize</t>
+  </si>
+  <si>
+    <t>Smokescreen</t>
+  </si>
+  <si>
+    <t>Confuse Ray</t>
+  </si>
+  <si>
+    <t>Defense Curl</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Light Screen</t>
+  </si>
+  <si>
+    <t>Haze</t>
+  </si>
+  <si>
+    <t>Reflect</t>
+  </si>
+  <si>
+    <t>Focus Energy</t>
+  </si>
+  <si>
+    <t>Metronome</t>
+  </si>
+  <si>
+    <t>Lick</t>
+  </si>
+  <si>
+    <t>Sludge</t>
+  </si>
+  <si>
+    <t>Fire Blast</t>
+  </si>
+  <si>
+    <t>Waterfall</t>
+  </si>
+  <si>
+    <t>Swift</t>
+  </si>
+  <si>
+    <t>Skull Bash</t>
+  </si>
+  <si>
+    <t>Amnesia</t>
+  </si>
+  <si>
+    <t>High Jump Kick</t>
+  </si>
+  <si>
+    <t>Glare</t>
+  </si>
+  <si>
+    <t>Dream Eater</t>
+  </si>
+  <si>
+    <t>Poison Gas</t>
+  </si>
+  <si>
+    <t>Leech Life</t>
+  </si>
+  <si>
+    <t>Lovely Kiss</t>
+  </si>
+  <si>
+    <t>Transform</t>
+  </si>
+  <si>
+    <t>Dizzy Punch</t>
+  </si>
+  <si>
+    <t>Spore</t>
+  </si>
+  <si>
+    <t>Splash</t>
+  </si>
+  <si>
+    <t>Acid Armor</t>
+  </si>
+  <si>
+    <t>Crabhammer</t>
+  </si>
+  <si>
+    <t>Explosion</t>
+  </si>
+  <si>
+    <t>Bonemerang</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>Rock Slide</t>
+  </si>
+  <si>
+    <t>Hyper Fang</t>
+  </si>
+  <si>
+    <t>Conversion</t>
+  </si>
+  <si>
+    <t>Tri Attack</t>
+  </si>
+  <si>
+    <t>Super Fang</t>
+  </si>
+  <si>
+    <t>Slash</t>
+  </si>
+  <si>
+    <t>Substitute</t>
+  </si>
+  <si>
+    <t>Struggle</t>
+  </si>
+  <si>
+    <t>Expansion</t>
+  </si>
+  <si>
+    <t>Triple Kick</t>
+  </si>
+  <si>
+    <t>Tutor</t>
+  </si>
+  <si>
+    <t>Flame Wheel</t>
+  </si>
+  <si>
+    <t>Flail</t>
+  </si>
+  <si>
+    <t>Protect</t>
+  </si>
+  <si>
+    <t>Mach Punch</t>
+  </si>
+  <si>
+    <t>Belly Drum</t>
+  </si>
+  <si>
+    <t>Sludge Bomb</t>
+  </si>
+  <si>
+    <t>Icy Wind</t>
+  </si>
+  <si>
+    <t>Outrage</t>
+  </si>
+  <si>
+    <t>Sandstorm</t>
+  </si>
+  <si>
+    <t>Charm</t>
+  </si>
+  <si>
+    <t>Rollout</t>
+  </si>
+  <si>
+    <t>Fury Cutter</t>
+  </si>
+  <si>
+    <t>Heal Bell</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>Frustration</t>
+  </si>
+  <si>
+    <t>Dynamic Punch</t>
+  </si>
+  <si>
+    <t>Megahorn</t>
+  </si>
+  <si>
+    <t>Dragon Breath</t>
+  </si>
+  <si>
+    <t>Encore</t>
+  </si>
+  <si>
+    <t>Pursuit</t>
+  </si>
+  <si>
+    <t>Rapid Spin</t>
+  </si>
+  <si>
+    <t>Iron Tail</t>
+  </si>
+  <si>
+    <t>Metal Claw</t>
+  </si>
+  <si>
+    <t>Synthesis</t>
+  </si>
+  <si>
+    <t>Cross Chop</t>
+  </si>
+  <si>
+    <t>Rain Dance</t>
+  </si>
+  <si>
+    <t>Sunny Day</t>
+  </si>
+  <si>
+    <t>Crunch</t>
+  </si>
+  <si>
+    <t>Mirror Coat</t>
+  </si>
+  <si>
+    <t>Extreme Speed</t>
+  </si>
+  <si>
+    <t>Ancient Power</t>
+  </si>
+  <si>
+    <t>Shadow Ball</t>
+  </si>
+  <si>
+    <t>Whirlpool</t>
+  </si>
+  <si>
+    <t>Fake Out</t>
+  </si>
+  <si>
+    <t>Hail</t>
+  </si>
+  <si>
+    <t>Will-O-Wisp</t>
+  </si>
+  <si>
+    <t>Facade</t>
+  </si>
+  <si>
+    <t>Taunt</t>
+  </si>
+  <si>
+    <t>Helping Hand</t>
+  </si>
+  <si>
+    <t>Wish</t>
+  </si>
+  <si>
+    <t>Superpower</t>
+  </si>
+  <si>
+    <t>Recycle</t>
+  </si>
+  <si>
+    <t>Brick Break</t>
+  </si>
+  <si>
+    <t>Yawn</t>
+  </si>
+  <si>
+    <t>Knock Off</t>
+  </si>
+  <si>
+    <t>Hyper Voice</t>
+  </si>
+  <si>
+    <t>Poison Fang</t>
+  </si>
+  <si>
+    <t>Meteor Mash</t>
+  </si>
+  <si>
+    <t>Weather Ball</t>
+  </si>
+  <si>
+    <t>Signal Beam</t>
+  </si>
+  <si>
+    <t>Aerial Ace</t>
+  </si>
+  <si>
+    <t>Icicle Spear</t>
+  </si>
+  <si>
+    <t>Bulk Up</t>
+  </si>
+  <si>
+    <t>Volt Tackle</t>
+  </si>
+  <si>
+    <t>Calm Mind</t>
+  </si>
+  <si>
+    <t>Leaf Blade</t>
+  </si>
+  <si>
+    <t>Dragon Dance</t>
+  </si>
+  <si>
+    <t>Rock Blast</t>
+  </si>
+  <si>
+    <t>Water Pulse</t>
+  </si>
+  <si>
+    <t>Roost</t>
+  </si>
+  <si>
+    <t>Gyro Ball</t>
+  </si>
+  <si>
+    <t>Feint</t>
+  </si>
+  <si>
+    <t>U-turn</t>
+  </si>
+  <si>
+    <t>Close Combat</t>
+  </si>
+  <si>
+    <t>Sucker Punch</t>
+  </si>
+  <si>
+    <t>Flare Blitz</t>
+  </si>
+  <si>
+    <t>Poison Jab</t>
+  </si>
+  <si>
+    <t>Dark Pulse</t>
+  </si>
+  <si>
+    <t>Night Slash</t>
+  </si>
+  <si>
+    <t>Aqua Tail</t>
+  </si>
+  <si>
+    <t>Seed Bomb</t>
+  </si>
+  <si>
+    <t>Air Slash</t>
+  </si>
+  <si>
+    <t>X-Scissor</t>
+  </si>
+  <si>
+    <t>Bug Buzz</t>
+  </si>
+  <si>
+    <t>Dragon Pulse</t>
+  </si>
+  <si>
+    <t>Focus Blast</t>
+  </si>
+  <si>
+    <t>Energy Ball</t>
+  </si>
+  <si>
+    <t>Brave Bird</t>
+  </si>
+  <si>
+    <t>Earth Power</t>
+  </si>
+  <si>
+    <t>Nasty Plot</t>
+  </si>
+  <si>
+    <t>Bullet Punch</t>
+  </si>
+  <si>
+    <t>Avalanche</t>
+  </si>
+  <si>
+    <t>Ice Shard</t>
+  </si>
+  <si>
+    <t>Psycho Cut</t>
+  </si>
+  <si>
+    <t>Zen Headbutt</t>
+  </si>
+  <si>
+    <t>Flash Cannon</t>
+  </si>
+  <si>
+    <t>Trick Room</t>
+  </si>
+  <si>
+    <t>Leaf Storm</t>
+  </si>
+  <si>
+    <t>Power Whip</t>
+  </si>
+  <si>
+    <t>Rock Wrecker</t>
+  </si>
+  <si>
+    <t>Cross Poison</t>
+  </si>
+  <si>
+    <t>Gunk Shot</t>
+  </si>
+  <si>
+    <t>Iron Head</t>
+  </si>
+  <si>
+    <t>Stone Edge</t>
+  </si>
+  <si>
+    <t>Stealth Rock</t>
+  </si>
+  <si>
+    <t>Grass Knot</t>
+  </si>
+  <si>
+    <t>Bug Bite</t>
+  </si>
+  <si>
+    <t>Aqua Jet</t>
+  </si>
+  <si>
+    <t>Quiver Dance</t>
+  </si>
+  <si>
+    <t>Heavy Slam</t>
+  </si>
+  <si>
+    <t>Coil</t>
+  </si>
+  <si>
+    <t>Low Sweep</t>
+  </si>
+  <si>
+    <t>Foul Play</t>
+  </si>
+  <si>
+    <t>Clear Smog</t>
+  </si>
+  <si>
+    <t>Scald</t>
+  </si>
+  <si>
+    <t>Shell Smash</t>
+  </si>
+  <si>
+    <t>Hex</t>
+  </si>
+  <si>
+    <t>Volt Switch</t>
+  </si>
+  <si>
+    <t>Bulldoze</t>
+  </si>
+  <si>
+    <t>Dragon Tail</t>
+  </si>
+  <si>
+    <t>Wild Charge</t>
+  </si>
+  <si>
+    <t>Drill Run</t>
+  </si>
+  <si>
+    <t>Hurricane</t>
+  </si>
+  <si>
+    <t>Fell Stinger</t>
+  </si>
+  <si>
+    <t>Freeze-Dry</t>
+  </si>
+  <si>
+    <t>Disarming Voice</t>
+  </si>
+  <si>
+    <t>Play Rough</t>
+  </si>
+  <si>
+    <t>Fairy Wind</t>
+  </si>
+  <si>
+    <t>Moonblast</t>
+  </si>
+  <si>
+    <t>Dazzling Gleam</t>
+  </si>
+  <si>
+    <t>Aurora Veil</t>
+  </si>
+  <si>
+    <t>Shadow Bone</t>
+  </si>
+  <si>
+    <t>Liquidation</t>
+  </si>
+  <si>
+    <t>Double Iron Bash</t>
+  </si>
+  <si>
+    <t>Strange Steam</t>
+  </si>
+</sst>
+</file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -26,24 +1191,382 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
+    <cellStyle name="Check Cell" xfId="7" builtinId="23"/>
+    <cellStyle name="Heading 2" xfId="8" builtinId="17"/>
+    <cellStyle name="Note" xfId="9" builtinId="10"/>
+    <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
+    <cellStyle name="60% - Accent4" xfId="11" builtinId="44"/>
+    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9"/>
+    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="Title" xfId="16" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
+    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
+    <cellStyle name="Input" xfId="21" builtinId="20"/>
+    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
+    <cellStyle name="Good" xfId="23" builtinId="26"/>
+    <cellStyle name="Output" xfId="24" builtinId="21"/>
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bad" xfId="29" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
+    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
+    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
+    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF71ABDB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF6BF595"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFC9D9D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FC9D9D"/>
+      <color rgb="006BF595"/>
+      <color rgb="0071ABDB"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -92,7 +1615,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -127,7 +1650,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -301,20 +1824,5 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>